--- a/MainTop/29.05.2026 Макс Имена/print.xlsx
+++ b/MainTop/29.05.2026 Макс Имена/print.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\29.05.2026 Макс Имена\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxim\Documents\GitHub\Ozon_upload\MainTop\29.05.2026 Макс Имена\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E26A4BE8-BB8C-4E3D-9222-6308A9EAE6EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6771A735-FAA7-46C8-98B7-1F1A1C75349D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Товарный состав" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
